--- a/data/merged/2026-09-23/MERGED_US_Robot-Vacuum_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_US_Robot-Vacuum_2026-09-23.xlsx
@@ -3735,13 +3735,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3867,13 +3867,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3911,13 +3911,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3955,13 +3955,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3999,13 +3999,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4087,7 +4087,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4175,7 +4175,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -4263,13 +4263,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4307,13 +4307,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4483,13 +4483,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4571,13 +4571,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4659,13 +4659,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4709,7 +4709,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4747,13 +4747,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4797,7 +4797,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4923,13 +4923,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4973,7 +4973,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5061,7 +5061,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5430,94 +5430,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -6922,7 +6834,7 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B0CYHHPZHD</t>
         </is>
       </c>
       <c r="D8" s="14"/>
@@ -6935,23 +6847,23 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS Multi-Surface Floor Cleaning Solution, Compatible with DEEBOT X11 OMNI Cyclone / X9 PRO OMNI / T80 OMNI / T50 PRO OMN</t>
+          <t>Shark UR2360S Ultra Robot Vacuum, with Matrix Clean, Precision Mapping, 30-Day Capacity HEPA Bagless Self Empty Base, Self-Cl</t>
         </is>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0BCF8N3B4?psc=1</t>
+          <t>https://www.amazon.com/dp/B0CYHHPZHD?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71rCIJ-c23L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0BCF8N3B4</t>
+          <t>B0CYHHPZHD</t>
         </is>
       </c>
       <c r="M8" s="1"/>
@@ -6968,17 +6880,17 @@
       <c r="X8" s="15"/>
       <c r="Y8"/>
       <c r="Z8" s="19">
-        <v>24.99</v>
+        <v>148.95</v>
       </c>
       <c r="AA8"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8" s="20">
-        <v>1219</v>
+        <v>1124</v>
       </c>
       <c r="AE8"/>
       <c r="AF8" s="21">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="22">
         <v>0</v>
@@ -7030,7 +6942,7 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0DG5G9HQM</t>
         </is>
       </c>
       <c r="D9" s="14"/>
@@ -7043,23 +6955,23 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>eufy RoboVac Hard Floor Cleaning Solution (2 Bottles), Dilution Ratio 1:200, 473 ml, Floor Cleaner, Plant-Based,Compatible wi</t>
+          <t>eufy X10 Pro Omni Robot Vacuum and Mop, Dual Mops, 12 mm Auto-Lift, Whites8,000 Pa Suction, Carpet Detection, AI Obstacle A</t>
         </is>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C7C7PLLG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DG5G9HQM?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/618bqWHuoyL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0DG5G9HQM</t>
         </is>
       </c>
       <c r="M9" s="1"/>
@@ -7076,17 +6988,17 @@
       <c r="X9" s="15"/>
       <c r="Y9"/>
       <c r="Z9" s="19">
-        <v>29.99</v>
+        <v>449.99</v>
       </c>
       <c r="AA9"/>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9" s="20">
-        <v>1512</v>
+        <v>39249</v>
       </c>
       <c r="AE9"/>
       <c r="AF9" s="21">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -7138,7 +7050,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0CYHHPZHD</t>
+          <t>B0DHCJ571Z</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7151,23 +7063,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Shark UR2360S Ultra Robot Vacuum, with Matrix Clean, Precision Mapping, 30-Day Capacity HEPA Bagless Self Empty Base, Self-Cl</t>
+          <t>roborock Saros 10R Robot Vacuum and Mop, 22000Pa, Edge Cleanings3.14" Slim Design Reaches Under Furniture, Zero-Tangle Syst</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0CYHHPZHD?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DHCJ571Z?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71rCIJ-c23L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/619xjRMbkSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0CYHHPZHD</t>
+          <t>B0DHCJ571Z</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7184,13 +7096,13 @@
       <c r="X10" s="15"/>
       <c r="Y10"/>
       <c r="Z10" s="19">
-        <v>148.95</v>
+        <v>1099.99</v>
       </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>1124</v>
+        <v>5105</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
@@ -7246,7 +7158,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0DG5G9HQM</t>
+          <t>B0DSJF7ZDJ</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7259,23 +7171,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>eufy X10 Pro Omni Robot Vacuum and Mop, Dual Mops, 12 mm Auto-Lift, Whites8,000 Pa Suction, Carpet Detection, AI Obstacle A</t>
+          <t>roborock Q7 M5 Robot Vacuum and Mop Combo, 10,000Pa HyperForce SuctionsDual Anti-Tangle System, APP-Controlled Mopping, LiD</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DG5G9HQM?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DSJF7ZDJ?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/618bqWHuoyL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51ueKj89YaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0DG5G9HQM</t>
+          <t>B0DSJF7ZDJ</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7292,13 +7204,13 @@
       <c r="X11" s="15"/>
       <c r="Y11"/>
       <c r="Z11" s="19">
-        <v>449.99</v>
+        <v>149.98</v>
       </c>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>39249</v>
+        <v>4338</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
@@ -7354,7 +7266,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0DHCJ571Z</t>
+          <t>B0DSP8J476</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7367,23 +7279,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>roborock Saros 10R Robot Vacuum and Mop, 22000Pa, Edge Cleanings3.14" Slim Design Reaches Under Furniture, Zero-Tangle Syst</t>
+          <t>roborock Qrevo S5V Robot Vacuum and Mop, FlexiArm Edge Moppings12,000Pa, Dual Zero-Tangle System, Smart Obstacle Avoidance,</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DHCJ571Z?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DSP8J476?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/619xjRMbkSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51Br5OrimUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0DHCJ571Z</t>
+          <t>B0DSP8J476</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7400,17 +7312,17 @@
       <c r="X12" s="15"/>
       <c r="Y12"/>
       <c r="Z12" s="19">
-        <v>1099.99</v>
+        <v>499.98</v>
       </c>
       <c r="AA12"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>5105</v>
+        <v>1754</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
@@ -7462,7 +7374,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0DSJF7ZDJ</t>
+          <t>B0DV53XDDJ</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7475,23 +7387,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>roborock Q7 M5 Robot Vacuum and Mop Combo, 10,000Pa HyperForce SuctionsDual Anti-Tangle System, APP-Controlled Mopping, LiD</t>
+          <t>Tikom Robot Vacuum and Mop Combo, 5000Pa Robotic Vacuum Cleaner, 150 Min Max, App &amp; Remote Control, Ideal for Hard Floor, Car</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DSJF7ZDJ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DV53XDDJ?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51ueKj89YaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71lOhFFaWuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0DSJF7ZDJ</t>
+          <t>B0DV53XDDJ</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7508,17 +7420,17 @@
       <c r="X13" s="15"/>
       <c r="Y13"/>
       <c r="Z13" s="19">
-        <v>149.98</v>
+        <v>109.99</v>
       </c>
       <c r="AA13"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>4338</v>
+        <v>4798</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
@@ -7570,7 +7482,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0DSP8J476</t>
+          <t>B0DWFZ8Q7M</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7583,23 +7495,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo S5V Robot Vacuum and Mop, FlexiArm Edge Moppings12,000Pa, Dual Zero-Tangle System, Smart Obstacle Avoidance,</t>
+          <t>iRobot Roomba 105 Combo Robot Vacuum &amp; Mop with AutoEmpty Dock - Self-Empties for 75 Days, Intense Power-Lifting Suction, LiD</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DSP8J476?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DWFZ8Q7M?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51Br5OrimUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/815+tXB4eYL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0DSP8J476</t>
+          <t>B0DWFZ8Q7M</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7616,17 +7528,17 @@
       <c r="X14" s="15"/>
       <c r="Y14"/>
       <c r="Z14" s="19">
-        <v>499.98</v>
+        <v>299</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>1754</v>
+        <v>49353</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
@@ -7678,7 +7590,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0DV53XDDJ</t>
+          <t>B0DWG1K24K</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7691,23 +7603,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Tikom Robot Vacuum and Mop Combo, 5000Pa Robotic Vacuum Cleaner, 150 Min Max, App &amp; Remote Control, Ideal for Hard Floor, Car</t>
+          <t>iRobot Roomba 105 Vac Robot Vacuum with AutoEmpty Dock - Self-Empties for 75 Days, Easy to use, Intense Power-Lifting Suction</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DV53XDDJ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DWG1K24K?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71lOhFFaWuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81csaOROmzL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0DV53XDDJ</t>
+          <t>B0DWG1K24K</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7724,17 +7636,17 @@
       <c r="X15" s="15"/>
       <c r="Y15"/>
       <c r="Z15" s="19">
-        <v>109.99</v>
+        <v>449</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>4798</v>
+        <v>19207</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7786,7 +7698,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0DWFZ8Q7M</t>
+          <t>B0DWG2BB7X</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7799,23 +7711,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba 105 Combo Robot Vacuum &amp; Mop with AutoEmpty Dock - Self-Empties for 75 Days, Intense Power-Lifting Suction, LiD</t>
+          <t>iRobot Roomba 105 Combo Robot Vacuum &amp; Mop - Easy to use, Intense Power-Lifting Suction, LiDAR Navigation, Multiple Cleaning</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DWFZ8Q7M?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DWG2BB7X?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/815+tXB4eYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/811u3j1SXNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0DWFZ8Q7M</t>
+          <t>B0DWG2BB7X</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7832,17 +7744,17 @@
       <c r="X16" s="15"/>
       <c r="Y16"/>
       <c r="Z16" s="19">
-        <v>299</v>
+        <v>179</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>49353</v>
+        <v>26549</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -7894,7 +7806,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0DWG1K24K</t>
+          <t>B0DWX69JVG</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7907,23 +7819,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba 105 Vac Robot Vacuum with AutoEmpty Dock - Self-Empties for 75 Days, Easy to use, Intense Power-Lifting Suction</t>
+          <t>roborock Q7 M5+ Robot Vacuum and Mop, Up to 7-9 Weeks Self-Empty, 10000PasUpgraded from Q5 Max+, Dual Anti-Tangle System fo</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DWG1K24K?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DWX69JVG?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81csaOROmzL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61EOq1YWmnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0DWG1K24K</t>
+          <t>B0DWX69JVG</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7940,13 +7852,13 @@
       <c r="X17" s="15"/>
       <c r="Y17"/>
       <c r="Z17" s="19">
-        <v>449</v>
+        <v>299.99</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>19207</v>
+        <v>25367</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
@@ -8002,7 +7914,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0DWG2BB7X</t>
+          <t>B0DX1DQKMD</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8015,23 +7927,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba 105 Combo Robot Vacuum &amp; Mop - Easy to use, Intense Power-Lifting Suction, LiDAR Navigation, Multiple Cleaning</t>
+          <t>roborock Qrevo CurvX Robot Vacuum and Mop, 22,000Pa Suctions3.14’’ Slim, Zero-Tangling, Reactive AI Obstacle Recognition, A</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DWG2BB7X?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DX1DQKMD?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/811u3j1SXNL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51GvwytZMFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0DWG2BB7X</t>
+          <t>B0DX1DQKMD</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8048,17 +7960,17 @@
       <c r="X18" s="15"/>
       <c r="Y18"/>
       <c r="Z18" s="19">
-        <v>179</v>
+        <v>949.99</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>26549</v>
+        <v>1708</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8110,7 +8022,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0DWX69JVG</t>
+          <t>B0DX6KZR9T</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8123,23 +8035,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>roborock Q7 M5+ Robot Vacuum and Mop, Up to 7-9 Weeks Self-Empty, 10000PasUpgraded from Q5 Max+, Dual Anti-Tangle System fo</t>
+          <t>iRobot Roomba 105 Vac Robot Vacuum - Easy to use, Intense Power-Lifting Suction, LiDAR Navigation, Multi-Surface Cleaning, Cl</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DWX69JVG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0DX6KZR9T?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61EOq1YWmnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71GZCWlJ6NL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0DWX69JVG</t>
+          <t>B0DX6KZR9T</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8156,17 +8068,17 @@
       <c r="X19" s="15"/>
       <c r="Y19"/>
       <c r="Z19" s="19">
-        <v>299.99</v>
+        <v>149</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>25367</v>
+        <v>31596</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8218,7 +8130,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0DX1DQKMD</t>
+          <t>B0F3WQTM9Q</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8231,23 +8143,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo CurvX Robot Vacuum and Mop, 22,000Pa Suctions3.14’’ Slim, Zero-Tangling, Reactive AI Obstacle Recognition, A</t>
+          <t>MOVA V50 Ultra Complete Robot Vacuum and Mop, 24,000Pa, Zero-Tanglings2.28in Obstacle Overcoming, FlexiRise Navigation, 176</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DX1DQKMD?psc=1</t>
+          <t>https://www.amazon.com/dp/B0F3WQTM9Q?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51GvwytZMFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61yh7O-JBSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0DX1DQKMD</t>
+          <t>B0F3WQTM9Q</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8264,17 +8176,17 @@
       <c r="X20" s="15"/>
       <c r="Y20"/>
       <c r="Z20" s="19">
-        <v>949.99</v>
+        <v>759.05</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>1708</v>
+        <v>182</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8326,7 +8238,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0DX6KZR9T</t>
+          <t>B0F4DKGRDN</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8339,23 +8251,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba 105 Vac Robot Vacuum - Easy to use, Intense Power-Lifting Suction, LiDAR Navigation, Multi-Surface Cleaning, Cl</t>
+          <t>ILIFE V2 Robot Vacuum Cleaner, Tangle-Free Suction, Whites120 Mins Runtime, Remote Control, Schedule, Slim, Self-Charging R</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0DX6KZR9T?psc=1</t>
+          <t>https://www.amazon.com/dp/B0F4DKGRDN?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71GZCWlJ6NL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Fss4uOG+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0DX6KZR9T</t>
+          <t>B0F4DKGRDN</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8372,13 +8284,13 @@
       <c r="X21" s="15"/>
       <c r="Y21"/>
       <c r="Z21" s="19">
-        <v>149</v>
+        <v>84.99</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>31596</v>
+        <v>24389</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
@@ -8434,7 +8346,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0F3WQTM9Q</t>
+          <t>B0FCX5ZH4L</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8447,23 +8359,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>MOVA V50 Ultra Complete Robot Vacuum and Mop, 24,000Pa, Zero-Tanglings2.28in Obstacle Overcoming, FlexiRise Navigation, 176</t>
+          <t>Tikom Robot Vacuum and Mop Combo, 6000Pa Automatic Robotic Vacuum Cleaner, Smart Mapping, 150 Min Max, Ideal for Pet Hair, Ha</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0F3WQTM9Q?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FCX5ZH4L?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61yh7O-JBSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71MTI9IDzXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0F3WQTM9Q</t>
+          <t>B0FCX5ZH4L</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8480,17 +8392,17 @@
       <c r="X22" s="15"/>
       <c r="Y22"/>
       <c r="Z22" s="19">
-        <v>759.05</v>
+        <v>149.99</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>182</v>
+        <v>355</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8542,7 +8454,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0F4DKGRDN</t>
+          <t>B0FDX7GFQX</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8555,23 +8467,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>ILIFE V2 Robot Vacuum Cleaner, Tangle-Free Suction, Whites120 Mins Runtime, Remote Control, Schedule, Slim, Self-Charging R</t>
+          <t>Shark Matrix Plus Robot Vacuum and Mop,UR2650WSsSonic Mopping, Matrix Clean, CleanEdge, HEPA 30-Day Self-Empty Base, 360° L</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0F4DKGRDN?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FDX7GFQX?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Fss4uOG+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71X5SuvZ-6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0F4DKGRDN</t>
+          <t>B0FDX7GFQX</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8588,17 +8500,17 @@
       <c r="X23" s="15"/>
       <c r="Y23"/>
       <c r="Z23" s="19">
-        <v>84.99</v>
+        <v>289</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>24389</v>
+        <v>36004</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8650,7 +8562,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0FCX5ZH4L</t>
+          <t>B0FK2HPNCB</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8663,23 +8575,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Tikom Robot Vacuum and Mop Combo, 6000Pa Automatic Robotic Vacuum Cleaner, Smart Mapping, 150 Min Max, Ideal for Pet Hair, Ha</t>
+          <t>eufy E25 Robot Vacuum and Mop Combo, 20,000 Pa, HydroJet Roller MopsExtendable Side Brush, Zero-Tangle Design, All-in-One S</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FCX5ZH4L?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FK2HPNCB?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71MTI9IDzXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61HYCNbUjAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0FCX5ZH4L</t>
+          <t>B0FK2HPNCB</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8696,17 +8608,17 @@
       <c r="X24" s="15"/>
       <c r="Y24"/>
       <c r="Z24" s="19">
-        <v>149.99</v>
+        <v>599.98</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>355</v>
+        <v>54027</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -8758,7 +8670,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0FDX7GFQX</t>
+          <t>B0FKH1RW65</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8771,23 +8683,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Shark Matrix Plus Robot Vacuum and Mop,UR2650WSsSonic Mopping, Matrix Clean, CleanEdge, HEPA 30-Day Self-Empty Base, 360° L</t>
+          <t>Tikom Robot Vacuum and Mop, Robotic Vacuum Cleaner with Self-Emptying Bases6000Pa, 90 Days Capacity, LiDAR Navigation, Home</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FDX7GFQX?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FKH1RW65?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71X5SuvZ-6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/712+1GJM3rL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0FDX7GFQX</t>
+          <t>B0FKH1RW65</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8804,17 +8716,17 @@
       <c r="X25" s="15"/>
       <c r="Y25"/>
       <c r="Z25" s="19">
-        <v>289</v>
+        <v>208.97</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>36004</v>
+        <v>631</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8866,7 +8778,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0FK2HPNCB</t>
+          <t>B0FSJPFDPV</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8879,23 +8791,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>eufy E25 Robot Vacuum and Mop Combo, 20,000 Pa, HydroJet Roller MopsExtendable Side Brush, Zero-Tangle Design, All-in-One S</t>
+          <t>dreame L40 Ultra Gen 2 Robot Vacuum and Mop with 25,000Pa SuctionsExtendable Side Brush &amp; Mop, All-in-One Self-Emptying &amp; C</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FK2HPNCB?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FSJPFDPV?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61HYCNbUjAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61hMADKz9DL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0FK2HPNCB</t>
+          <t>B0FSJPFDPV</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8912,17 +8824,17 @@
       <c r="X26" s="15"/>
       <c r="Y26"/>
       <c r="Z26" s="19">
-        <v>599.98</v>
+        <v>569.99</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>54027</v>
+        <v>581</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8974,7 +8886,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0FKH1RW65</t>
+          <t>B0FXG2BDTJ</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8987,23 +8899,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Tikom Robot Vacuum and Mop, Robotic Vacuum Cleaner with Self-Emptying Bases6000Pa, 90 Days Capacity, LiDAR Navigation, Home</t>
+          <t>roborock Qrevo Curv 2 Flow 2026 New Robot Vacuum and Mop, 20,000 Pa, SpiraFlow Real-Time Self-Cleaning Roller Mop, Dual Zero-</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FKH1RW65?psc=1</t>
+          <t>https://www.amazon.com/dp/B0FXG2BDTJ?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/712+1GJM3rL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/615YZDkBQZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0FKH1RW65</t>
+          <t>B0FXG2BDTJ</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -9020,17 +8932,17 @@
       <c r="X27" s="15"/>
       <c r="Y27"/>
       <c r="Z27" s="19">
-        <v>208.97</v>
+        <v>799.99</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>631</v>
+        <v>1369</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9082,7 +8994,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FSJPFDPV</t>
+          <t>B0G1RZHD6Q</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9095,23 +9007,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>dreame L40 Ultra Gen 2 Robot Vacuum and Mop with 25,000Pa SuctionsExtendable Side Brush &amp; Mop, All-in-One Self-Emptying &amp; C</t>
+          <t>MOVA P10 Pro Ultra Gen 2 Robot Vacuum and Mop 26000Pa Suction 2026 Upgradeds212°F Hot Water Auto Mop Washing, 1-Hour Hot Ai</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FSJPFDPV?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G1RZHD6Q?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61hMADKz9DL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/513N30HO1wL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FSJPFDPV</t>
+          <t>B0G1RZHD6Q</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9128,17 +9040,17 @@
       <c r="X28" s="15"/>
       <c r="Y28"/>
       <c r="Z28" s="19">
-        <v>569.99</v>
+        <v>499</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>581</v>
+        <v>330</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9190,7 +9102,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FXG2BDTJ</t>
+          <t>B0G5X4H4PS</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9203,23 +9115,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>roborock Qrevo Curv 2 Flow 2026 New Robot Vacuum and Mop, 20,000 Pa, SpiraFlow Real-Time Self-Cleaning Roller Mop, Dual Zero-</t>
+          <t>dreame X60 Max Ultra Complete Robot Vacuum and Mop, Dual Al Camerass3.47in(8.8cm) Obstacle Crossing for Carpet, 35,000Pa Su</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0FXG2BDTJ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G5X4H4PS?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/615YZDkBQZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81e0h-0ULTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FXG2BDTJ</t>
+          <t>B0G5X4H4PS</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9236,17 +9148,17 @@
       <c r="X29" s="15"/>
       <c r="Y29"/>
       <c r="Z29" s="19">
-        <v>799.99</v>
+        <v>1699.99</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>1369</v>
+        <v>258</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9298,7 +9210,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0G1RZHD6Q</t>
+          <t>B0G5Y3LN8M</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9311,23 +9223,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>MOVA P10 Pro Ultra Gen 2 Robot Vacuum and Mop 26000Pa Suction 2026 Upgradeds212°F Hot Water Auto Mop Washing, 1-Hour Hot Ai</t>
+          <t>dreame D20 Air Plus Robot Vacuum and Mop, 20,000Pa Powerful Suctions120-Day Self-Emptying with 4L Dust Bag, Anti-Tangling T</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G1RZHD6Q?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G5Y3LN8M?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/513N30HO1wL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/617kvBl-umL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0G1RZHD6Q</t>
+          <t>B0G5Y3LN8M</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9344,17 +9256,17 @@
       <c r="X30" s="15"/>
       <c r="Y30"/>
       <c r="Z30" s="19">
-        <v>499</v>
+        <v>227.99</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>330</v>
+        <v>3636</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -9406,7 +9318,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0G5X4H4PS</t>
+          <t>B0G5YDVR99</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9419,23 +9331,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>dreame X60 Max Ultra Complete Robot Vacuum and Mop, Dual Al Camerass3.47in(8.8cm) Obstacle Crossing for Carpet, 35,000Pa Su</t>
+          <t>ILIFE A30s Robot Vacuum, 10000Pa Max SuctionsLiDAR Navigation, Home Mapping, No-Go Zone, 150 Mins, App, Voice and Remote Co</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G5X4H4PS?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G5YDVR99?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81e0h-0ULTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61XtYzJjN0L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0G5X4H4PS</t>
+          <t>B0G5YDVR99</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9452,17 +9364,17 @@
       <c r="X31" s="15"/>
       <c r="Y31"/>
       <c r="Z31" s="19">
-        <v>1699.99</v>
+        <v>138.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>258</v>
+        <v>1780</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9514,7 +9426,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0G5Y3LN8M</t>
+          <t>B0G64MM1HM</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9527,23 +9439,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>dreame D20 Air Plus Robot Vacuum and Mop, 20,000Pa Powerful Suctions120-Day Self-Emptying with 4L Dust Bag, Anti-Tangling T</t>
+          <t>roborock Saros 20 Robot Vacuum and Mop, 36000 Pa, 300+ Obstacle Avoidances3.14'' Ultra Slim, 3.46 in Double-Layer Threshold</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G5Y3LN8M?psc=1</t>
+          <t>https://www.amazon.com/dp/B0G64MM1HM?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/617kvBl-umL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/612SjLhCvdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0G5Y3LN8M</t>
+          <t>B0G64MM1HM</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9560,13 +9472,13 @@
       <c r="X32" s="15"/>
       <c r="Y32"/>
       <c r="Z32" s="19">
-        <v>227.99</v>
+        <v>1599.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>3636</v>
+        <v>4485</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
@@ -9622,7 +9534,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0G5YDVR99</t>
+          <t>B0GDXV2KJ4</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9635,23 +9547,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>ILIFE A30s Robot Vacuum, 10000Pa Max SuctionsLiDAR Navigation, Home Mapping, No-Go Zone, 150 Mins, App, Voice and Remote Co</t>
+          <t>ROPVACNIC Robot Vacuum and Mop Combo 5200Pa Suction Robotic CleanersSelf-charging, app control, personalized cleaning adjus</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G5YDVR99?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GDXV2KJ4?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61XtYzJjN0L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/518+BuiWh6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0G5YDVR99</t>
+          <t>B0GDXV2KJ4</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9668,17 +9580,17 @@
       <c r="X33" s="15"/>
       <c r="Y33"/>
       <c r="Z33" s="19">
-        <v>138.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>1780</v>
+        <v>2062</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9730,7 +9642,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0G64MM1HM</t>
+          <t>B0GGRSMXKN</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9743,23 +9655,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>roborock Saros 20 Robot Vacuum and Mop, 36000 Pa, 300+ Obstacle Avoidances3.14'' Ultra Slim, 3.46 in Double-Layer Threshold</t>
+          <t>roborock 2026 New Qrevo S Pro Robot Vacuum and Mop, 18,500Pa SuctionsMultifunctional Dock with 167℉ Mop Self-Cleaning, Smar</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0G64MM1HM?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GGRSMXKN?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/612SjLhCvdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61dUJLJCe5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0G64MM1HM</t>
+          <t>B0GGRSMXKN</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9776,17 +9688,17 @@
       <c r="X34" s="15"/>
       <c r="Y34"/>
       <c r="Z34" s="19">
-        <v>1599.99</v>
+        <v>499.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>4485</v>
+        <v>6348</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -9838,7 +9750,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GDXV2KJ4</t>
+          <t>B0GHWNW6D1</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9851,23 +9763,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>ROPVACNIC Robot Vacuum and Mop Combo 5200Pa Suction Robotic CleanersSelf-charging, app control, personalized cleaning adjus</t>
+          <t>ILIFE V5s Max Robot Vacuum, 4000Pa Strong Suction, Gyro Navigations2.4G WiFi/App/Alexa/Remote Control, Self-Charging Roboti</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GDXV2KJ4?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GHWNW6D1?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/518+BuiWh6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71-rCKaA69L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GDXV2KJ4</t>
+          <t>B0GHWNW6D1</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9884,17 +9796,17 @@
       <c r="X35" s="15"/>
       <c r="Y35"/>
       <c r="Z35" s="19">
-        <v>99.99</v>
+        <v>129.98</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>2062</v>
+        <v>11997</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9946,7 +9858,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GGRSMXKN</t>
+          <t>B0GHY7VT3Y</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9959,23 +9871,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>roborock 2026 New Qrevo S Pro Robot Vacuum and Mop, 18,500Pa SuctionsMultifunctional Dock with 167℉ Mop Self-Cleaning, Smar</t>
+          <t>ECOVACS DEEBOT T80S Omni Robot Vacuum and Mop, 24800Pa Suction, 2026 NewsTruEdge Instant Self-Cleaning OZMO Roller, Triple</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GGRSMXKN?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GHY7VT3Y?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61dUJLJCe5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61QqsFnb0lL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GGRSMXKN</t>
+          <t>B0GHY7VT3Y</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9992,17 +9904,17 @@
       <c r="X36" s="15"/>
       <c r="Y36"/>
       <c r="Z36" s="19">
-        <v>499.99</v>
+        <v>478.99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>6348</v>
+        <v>803</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10054,7 +9966,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GHWNW6D1</t>
+          <t>B0GJDHYRLR</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10067,23 +9979,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>ILIFE V5s Max Robot Vacuum, 4000Pa Strong Suction, Gyro Navigations2.4G WiFi/App/Alexa/Remote Control, Self-Charging Roboti</t>
+          <t>ECOVACS WINBOT MINI 2 Compact Window Cleaning Robot with Edge Cleanings8000Pa Suction, Ultrasonic Spray, WIN-SLAM 4.0 Navig</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GHWNW6D1?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GJDHYRLR?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71-rCKaA69L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61egoqFdtGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GHWNW6D1</t>
+          <t>B0GJDHYRLR</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10100,17 +10012,17 @@
       <c r="X37" s="15"/>
       <c r="Y37"/>
       <c r="Z37" s="19">
-        <v>129.98</v>
+        <v>189</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>11997</v>
+        <v>198</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10162,7 +10074,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GHY7VT3Y</t>
+          <t>B0GQSDKJ39</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10175,23 +10087,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS DEEBOT T80S Omni Robot Vacuum and Mop, 24800Pa Suction, 2026 NewsTruEdge Instant Self-Cleaning OZMO Roller, Triple</t>
+          <t>dreame D30 Ultra CE Robot Vacuum and Mop, 25,000Pa Powerful Suctions0.41in Mop Lifting, Multifunctional Base Station, Auto</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GHY7VT3Y?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GQSDKJ39?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61QqsFnb0lL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61s+Q1jMuRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GHY7VT3Y</t>
+          <t>B0GQSDKJ39</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10208,17 +10120,17 @@
       <c r="X38" s="15"/>
       <c r="Y38"/>
       <c r="Z38" s="19">
-        <v>478.99</v>
+        <v>459.98</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>803</v>
+        <v>1829</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10270,7 +10182,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GJDHYRLR</t>
+          <t>B0GXFHY7Y2</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10283,23 +10195,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>ECOVACS WINBOT MINI 2 Compact Window Cleaning Robot with Edge Cleanings8000Pa Suction, Ultrasonic Spray, WIN-SLAM 4.0 Navig</t>
+          <t>roborock 2026 New Qrevo 2 Pro Robot Vacuum and Mop, 20,000Pa SuctionsFlexiArm Edge Mopping, Zero-Tangle, High-Temperature M</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GJDHYRLR?psc=1</t>
+          <t>https://www.amazon.com/dp/B0GXFHY7Y2?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61egoqFdtGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51KNygIh2fL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GJDHYRLR</t>
+          <t>B0GXFHY7Y2</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10316,17 +10228,17 @@
       <c r="X39" s="15"/>
       <c r="Y39"/>
       <c r="Z39" s="19">
-        <v>189</v>
+        <v>549.98</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>198</v>
+        <v>964</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10378,7 +10290,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GQSDKJ39</t>
+          <t>B0H34TVVR6</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10391,23 +10303,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>dreame D30 Ultra CE Robot Vacuum and Mop, 25,000Pa Powerful Suctions0.41in Mop Lifting, Multifunctional Base Station, Auto</t>
+          <t>iRobot Roomba Max 775 Pet Robot Vacuum &amp; Mop Combo, 30,000Pa Suction, Heated Mopping, Self-Cleaning Roller Mop, Retracting Mo</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GQSDKJ39?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H34TVVR6?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61s+Q1jMuRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71NYsJ8ainL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GQSDKJ39</t>
+          <t>B0H34TVVR6</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10424,17 +10336,17 @@
       <c r="X40" s="15"/>
       <c r="Y40"/>
       <c r="Z40" s="19">
-        <v>459.98</v>
+        <v>799.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>1829</v>
+        <v>4931</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10486,7 +10398,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0GXFHY7Y2</t>
+          <t>B0H34WLWY4</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10499,23 +10411,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>roborock 2026 New Qrevo 2 Pro Robot Vacuum and Mop, 20,000Pa SuctionsFlexiArm Edge Mopping, Zero-Tangle, High-Temperature M</t>
+          <t>iRobot Roomba Plus 575X Combo Robot + AutoWash Dock, Self‑Cleans, Heated Wash &amp; Heated Dry, Auto‑Empties up to 90 Days, 3.2X</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0GXFHY7Y2?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H34WLWY4?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51KNygIh2fL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/710m8dFaC3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0GXFHY7Y2</t>
+          <t>B0H34WLWY4</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10532,17 +10444,17 @@
       <c r="X41" s="15"/>
       <c r="Y41"/>
       <c r="Z41" s="19">
-        <v>549.98</v>
+        <v>699.99</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>964</v>
+        <v>12</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10594,7 +10506,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H34TVVR6</t>
+          <t>B0H3P3DTCD</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10607,23 +10519,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba Max 775 Pet Robot Vacuum &amp; Mop Combo, 30,000Pa Suction, Heated Mopping, Self-Cleaning Roller Mop, Retracting Mo</t>
+          <t>VONKO Robot Vacuum and Mop, 8000Pa, Self-Emptying, LiDAR NavigationsUp to 60 Days Hands-Free, Smart Mapping, App &amp; Alexa Co</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H34TVVR6?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H3P3DTCD?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71NYsJ8ainL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71URtTaMQKL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H34TVVR6</t>
+          <t>B0H3P3DTCD</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10640,17 +10552,17 @@
       <c r="X42" s="15"/>
       <c r="Y42"/>
       <c r="Z42" s="19">
-        <v>799.99</v>
+        <v>199.98</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="20">
-        <v>4931</v>
+        <v>173</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AG42" s="22">
         <v>0</v>
@@ -10702,7 +10614,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H34WLWY4</t>
+          <t>B0H41M32CZ</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10715,23 +10627,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba Plus 575X Combo Robot + AutoWash Dock, Self‑Cleans, Heated Wash &amp; Heated Dry, Auto‑Empties up to 90 Days, 3.2X</t>
+          <t>Bagotte Robot Vacuum and Mop Combo,6000Pa LiDAR Navigation Robotic Vacuum Cleaner,Self-Emptying Station for 90 Days,Wi-Fi/App</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H34WLWY4?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H41M32CZ?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710m8dFaC3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71xrflP9WIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H34WLWY4</t>
+          <t>B0H41M32CZ</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10748,17 +10660,17 @@
       <c r="X43" s="15"/>
       <c r="Y43"/>
       <c r="Z43" s="19">
-        <v>699.99</v>
+        <v>239.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="20">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="21">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
@@ -10810,7 +10722,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H3P3DTCD</t>
+          <t>B0H4WXSXHS</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10823,23 +10735,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>VONKO Robot Vacuum and Mop, 8000Pa, Self-Emptying, LiDAR NavigationsUp to 60 Days Hands-Free, Smart Mapping, App &amp; Alexa Co</t>
+          <t>iRobot Roomba Max 715 Pet Robot Vacuum, 30,000Pa Suction, Dual Rubber Anti-Tangle Brushes &amp; Side Brush, 90 Days Self-Emptying</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H3P3DTCD?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H4WXSXHS?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71URtTaMQKL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71KKtInj20L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H3P3DTCD</t>
+          <t>B0H4WXSXHS</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10856,17 +10768,17 @@
       <c r="X44" s="15"/>
       <c r="Y44"/>
       <c r="Z44" s="19">
-        <v>199.98</v>
+        <v>599.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="20">
-        <v>173</v>
+        <v>2836</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
@@ -10918,7 +10830,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H41M32CZ</t>
+          <t>B0H7BHDLP3</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10931,23 +10843,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Bagotte Robot Vacuum and Mop Combo,6000Pa LiDAR Navigation Robotic Vacuum Cleaner,Self-Emptying Station for 90 Days,Wi-Fi/App</t>
+          <t>TRDIOL Robot Vacuum and Mop, 120-Day Self-Emptying with 6000Pa Suction, LiDAR Navigation &amp; Smart Mapping &amp; No-Go Zones, Anti-</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H41M32CZ?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H7BHDLP3?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71xrflP9WIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Y82wY-+9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H41M32CZ</t>
+          <t>B0H7BHDLP3</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10964,17 +10876,17 @@
       <c r="X45" s="15"/>
       <c r="Y45"/>
       <c r="Z45" s="19">
-        <v>239.99</v>
+        <v>239.98</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="20">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="21">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
@@ -11026,7 +10938,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0H4WXSXHS</t>
+          <t>B0H7S7DBCC</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -11039,23 +10951,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>iRobot Roomba Max 715 Pet Robot Vacuum, 30,000Pa Suction, Dual Rubber Anti-Tangle Brushes &amp; Side Brush, 90 Days Self-Emptying</t>
+          <t>MAMNV Robot Vacuum,11500Pa Suction,LiDAR Navigation,Self-Emptying,Pet Hairs90-Day Hands-Free Cleaning 160-Minute Long Runti</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H4WXSXHS?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H7S7DBCC?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71KKtInj20L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Ir2xpMGZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0H4WXSXHS</t>
+          <t>B0H7S7DBCC</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11072,17 +10984,17 @@
       <c r="X46" s="15"/>
       <c r="Y46"/>
       <c r="Z46" s="19">
-        <v>599.99</v>
+        <v>279.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="20">
-        <v>2836</v>
+        <v>1940</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
@@ -11134,7 +11046,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H7BHDLP3</t>
+          <t>B0HBQR6ZHF</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11147,23 +11059,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>TRDIOL Robot Vacuum and Mop, 120-Day Self-Emptying with 6000Pa Suction, LiDAR Navigation &amp; Smart Mapping &amp; No-Go Zones, Anti-</t>
+          <t>UMMUND Robot Vacuum and Mop Combo, 8000Pa Strong Suction 2 in 1 Vacuum Robot with Mopping, with Schedule, Wi-Fi/App/Remote, S</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H7BHDLP3?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HBQR6ZHF?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Y82wY-+9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81Z7yp-x1YL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H7BHDLP3</t>
+          <t>B0HBQR6ZHF</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11180,17 +11092,17 @@
       <c r="X47" s="15"/>
       <c r="Y47"/>
       <c r="Z47" s="19">
-        <v>239.98</v>
+        <v>125.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="20">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="21">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -11242,7 +11154,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H7S7DBCC</t>
+          <t>B0HF7K2ZKS</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11255,23 +11167,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>MAMNV Robot Vacuum,11500Pa Suction,LiDAR Navigation,Self-Emptying,Pet Hairs90-Day Hands-Free Cleaning 160-Minute Long Runti</t>
+          <t>XIEBro Robot Vacuum and Mop, 6500Pa Suction, 2 in 1 Robotic Vacuum with Gyro Inertial Navigation, 200 Min Runtime, App/Remote</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0H7S7DBCC?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HF7K2ZKS?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Ir2xpMGZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H7S7DBCC</t>
+          <t>B0HF7K2ZKS</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11288,17 +11200,17 @@
       <c r="X48" s="15"/>
       <c r="Y48"/>
       <c r="Z48" s="19">
-        <v>279.99</v>
+        <v>119.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="20">
-        <v>1940</v>
+        <v>18</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="21">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
@@ -11350,7 +11262,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0HBQR6ZHF</t>
+          <t>B0HFJCMP9T</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11363,23 +11275,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>UMMUND Robot Vacuum and Mop Combo, 8000Pa Strong Suction 2 in 1 Vacuum Robot with Mopping, with Schedule, Wi-Fi/App/Remote, S</t>
+          <t>Robot Vacuum and Mop Combo, 5000Pa Self-Charging Robotic Vacuum cleaner with Alexa &amp; App Control, 3-in-1 Robot Vacuum with Sm</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0HBQR6ZHF?psc=1</t>
+          <t>https://www.amazon.com/dp/B0HFJCMP9T?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81Z7yp-x1YL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0HBQR6ZHF</t>
+          <t>B0HFJCMP9T</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11396,17 +11308,17 @@
       <c r="X49" s="15"/>
       <c r="Y49"/>
       <c r="Z49" s="19">
-        <v>125.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="20">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="21">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
@@ -11451,222 +11363,6 @@
       <c r="BQ49" s="23"/>
       <c r="BR49"/>
     </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0HF7K2ZKS</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.comundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>XIEBro Robot Vacuum and Mop, 6500Pa Suction, 2 in 1 Robotic Vacuum with Gyro Inertial Navigation, 200 Min Runtime, App/Remote</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HF7K2ZKS?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0HF7K2ZKS</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50"/>
-      <c r="Z50" s="19">
-        <v>119.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="20">
-        <v>18</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="21">
-        <v>4.9</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="20"/>
-      <c r="AM50"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="20"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJCMP9T</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.comundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Robot Vacuum and Mop Combo, 5000Pa Self-Charging Robotic Vacuum cleaner with Alexa &amp; App Control, 3-in-1 Robot Vacuum with Sm</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0HFJCMP9T?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFJCMP9T</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19">
-        <v>99.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20">
-        <v>25</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -11701,228 +11397,218 @@
     <hyperlink ref="J7" r:id="rId28" tooltip="https://www.amazon.com/dp/B0B8B6N2G4?psc=1"/>
     <hyperlink ref="K7" r:id="rId29" tooltip="https://images-na.ssl-images-amazon.com/images/I/81ovo7-YW0L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L7" r:id="rId30" tooltip="https://www.amazon.com/dp/B0B8B6N2G4"/>
-    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
+    <hyperlink ref="C8" r:id="rId31" tooltip="https://www.amazon.com/dp/B0CYHHPZHD"/>
     <hyperlink ref="G8" r:id="rId32" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B0BCF8N3B4?psc=1"/>
-    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
+    <hyperlink ref="J8" r:id="rId33" tooltip="https://www.amazon.com/dp/B0CYHHPZHD?psc=1"/>
+    <hyperlink ref="K8" r:id="rId34" tooltip="https://images-na.ssl-images-amazon.com/images/I/71rCIJ-c23L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId35" tooltip="https://www.amazon.com/dp/B0CYHHPZHD"/>
+    <hyperlink ref="C9" r:id="rId36" tooltip="https://www.amazon.com/dp/B0DG5G9HQM"/>
     <hyperlink ref="G9" r:id="rId37" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B0C7C7PLLG?psc=1"/>
-    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B0CYHHPZHD"/>
+    <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.com/dp/B0DG5G9HQM?psc=1"/>
+    <hyperlink ref="K9" r:id="rId39" tooltip="https://images-na.ssl-images-amazon.com/images/I/618bqWHuoyL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.com/dp/B0DG5G9HQM"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.com/dp/B0DHCJ571Z"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B0CYHHPZHD?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/71rCIJ-c23L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B0CYHHPZHD"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0DG5G9HQM"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.com/dp/B0DHCJ571Z?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-na.ssl-images-amazon.com/images/I/619xjRMbkSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.com/dp/B0DHCJ571Z"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0DG5G9HQM?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/618bqWHuoyL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0DG5G9HQM"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0DHCJ571Z"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-na.ssl-images-amazon.com/images/I/51ueKj89YaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.com/dp/B0DSP8J476"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0DHCJ571Z?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/619xjRMbkSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0DHCJ571Z"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.com/dp/B0DSP8J476?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-na.ssl-images-amazon.com/images/I/51Br5OrimUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.com/dp/B0DSP8J476"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.com/dp/B0DV53XDDJ"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/51ueKj89YaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0DSJF7ZDJ"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0DSP8J476"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.com/dp/B0DV53XDDJ?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lOhFFaWuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.com/dp/B0DV53XDDJ"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0DSP8J476?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/51Br5OrimUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0DSP8J476"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0DV53XDDJ"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-na.ssl-images-amazon.com/images/I/815+tXB4eYL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.com/dp/B0DWG1K24K"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0DV53XDDJ?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/71lOhFFaWuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0DV53XDDJ"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.com/dp/B0DWG1K24K?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-na.ssl-images-amazon.com/images/I/81csaOROmzL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.com/dp/B0DWG1K24K"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.com/dp/B0DWG2BB7X"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/815+tXB4eYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0DWFZ8Q7M"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0DWG1K24K"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.com/dp/B0DWG2BB7X?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-na.ssl-images-amazon.com/images/I/811u3j1SXNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.com/dp/B0DWG2BB7X"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.com/dp/B0DWX69JVG"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0DWG1K24K?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/81csaOROmzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0DWG1K24K"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0DWG2BB7X"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.com/dp/B0DWX69JVG?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-na.ssl-images-amazon.com/images/I/61EOq1YWmnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.com/dp/B0DWX69JVG"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.com/dp/B0DX1DQKMD"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0DWG2BB7X?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/811u3j1SXNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0DWG2BB7X"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0DWX69JVG"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.com/dp/B0DX1DQKMD?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-na.ssl-images-amazon.com/images/I/51GvwytZMFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.com/dp/B0DX1DQKMD"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.com/dp/B0DX6KZR9T"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0DWX69JVG?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/61EOq1YWmnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0DWX69JVG"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0DX1DQKMD"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.com/dp/B0DX6KZR9T?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-na.ssl-images-amazon.com/images/I/71GZCWlJ6NL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.com/dp/B0DX6KZR9T"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0DX1DQKMD?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/51GvwytZMFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0DX1DQKMD"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0DX6KZR9T"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-na.ssl-images-amazon.com/images/I/61yh7O-JBSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.com/dp/B0F4DKGRDN"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0DX6KZR9T?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/71GZCWlJ6NL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0DX6KZR9T"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.com/dp/B0F4DKGRDN?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Fss4uOG+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.com/dp/B0F4DKGRDN"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/61yh7O-JBSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0F3WQTM9Q"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0F4DKGRDN"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-na.ssl-images-amazon.com/images/I/71MTI9IDzXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.com/dp/B0FDX7GFQX"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0F4DKGRDN?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Fss4uOG+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0F4DKGRDN"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.com/dp/B0FDX7GFQX?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-na.ssl-images-amazon.com/images/I/71X5SuvZ-6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.com/dp/B0FDX7GFQX"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.com/dp/B0FK2HPNCB"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/71MTI9IDzXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0FCX5ZH4L"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0FDX7GFQX"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.com/dp/B0FK2HPNCB?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HYCNbUjAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.com/dp/B0FK2HPNCB"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.com/dp/B0FKH1RW65"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0FDX7GFQX?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/71X5SuvZ-6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0FDX7GFQX"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0FK2HPNCB"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.com/dp/B0FKH1RW65?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-na.ssl-images-amazon.com/images/I/712+1GJM3rL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.com/dp/B0FKH1RW65"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.com/dp/B0FSJPFDPV"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0FK2HPNCB?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/61HYCNbUjAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0FK2HPNCB"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FKH1RW65"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.com/dp/B0FSJPFDPV?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-na.ssl-images-amazon.com/images/I/61hMADKz9DL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.com/dp/B0FSJPFDPV"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FKH1RW65?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/712+1GJM3rL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FKH1RW65"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0FSJPFDPV"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-na.ssl-images-amazon.com/images/I/615YZDkBQZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0FSJPFDPV?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/61hMADKz9DL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0FSJPFDPV"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-na.ssl-images-amazon.com/images/I/513N30HO1wL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.com/dp/B0G5X4H4PS"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/615YZDkBQZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0FXG2BDTJ"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.com/dp/B0G5X4H4PS?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-na.ssl-images-amazon.com/images/I/81e0h-0ULTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.com/dp/B0G5X4H4PS"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/513N30HO1wL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0G1RZHD6Q"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0G5X4H4PS"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-na.ssl-images-amazon.com/images/I/617kvBl-umL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.com/dp/B0G5YDVR99"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0G5X4H4PS?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/81e0h-0ULTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0G5X4H4PS"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.com/dp/B0G5YDVR99?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-na.ssl-images-amazon.com/images/I/61XtYzJjN0L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.com/dp/B0G5YDVR99"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.com/dp/B0G64MM1HM"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/617kvBl-umL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0G5Y3LN8M"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0G5YDVR99"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.com/dp/B0G64MM1HM?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-na.ssl-images-amazon.com/images/I/612SjLhCvdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.com/dp/B0G64MM1HM"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0G5YDVR99?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/61XtYzJjN0L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0G5YDVR99"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0G64MM1HM"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-na.ssl-images-amazon.com/images/I/518+BuiWh6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.com/dp/B0GGRSMXKN"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0G64MM1HM?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/612SjLhCvdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0G64MM1HM"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.com/dp/B0GGRSMXKN?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-na.ssl-images-amazon.com/images/I/61dUJLJCe5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.com/dp/B0GGRSMXKN"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.com/dp/B0GHWNW6D1"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/518+BuiWh6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GDXV2KJ4"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GGRSMXKN"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.com/dp/B0GHWNW6D1?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-na.ssl-images-amazon.com/images/I/71-rCKaA69L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.com/dp/B0GHWNW6D1"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GGRSMXKN?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/61dUJLJCe5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GGRSMXKN"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0GHWNW6D1"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-na.ssl-images-amazon.com/images/I/61QqsFnb0lL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.com/dp/B0GJDHYRLR"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0GHWNW6D1?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/71-rCKaA69L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0GHWNW6D1"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.com/dp/B0GJDHYRLR?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-na.ssl-images-amazon.com/images/I/61egoqFdtGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.com/dp/B0GJDHYRLR"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.com/dp/B0GQSDKJ39"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/61QqsFnb0lL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0GHY7VT3Y"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0GJDHYRLR"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.com/dp/B0GQSDKJ39?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-na.ssl-images-amazon.com/images/I/61s+Q1jMuRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.com/dp/B0GQSDKJ39"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0GJDHYRLR?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/61egoqFdtGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0GJDHYRLR"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0GQSDKJ39"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-na.ssl-images-amazon.com/images/I/51KNygIh2fL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.com/dp/B0H34TVVR6"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0GQSDKJ39?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/61s+Q1jMuRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0GQSDKJ39"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.com/dp/B0H34TVVR6?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NYsJ8ainL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.com/dp/B0H34TVVR6"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.com/dp/B0H34WLWY4"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/51KNygIh2fL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0GXFHY7Y2"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0H34TVVR6"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.com/dp/B0H34WLWY4?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/710m8dFaC3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.com/dp/B0H34WLWY4"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.com/dp/B0H3P3DTCD"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0H34TVVR6?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NYsJ8ainL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0H34TVVR6"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H34WLWY4"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.com/dp/B0H3P3DTCD?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-na.ssl-images-amazon.com/images/I/71URtTaMQKL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.com/dp/B0H3P3DTCD"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.com/dp/B0H41M32CZ"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H34WLWY4?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/710m8dFaC3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H34WLWY4"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H3P3DTCD"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.com/dp/B0H41M32CZ?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xrflP9WIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.com/dp/B0H41M32CZ"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.com/dp/B0H4WXSXHS"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H3P3DTCD?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71URtTaMQKL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H3P3DTCD"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H41M32CZ"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.com/dp/B0H4WXSXHS?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71KKtInj20L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.com/dp/B0H4WXSXHS"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.com/dp/B0H7BHDLP3"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H41M32CZ?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/71xrflP9WIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H41M32CZ"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0H4WXSXHS"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.com/dp/B0H7BHDLP3?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Y82wY-+9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.com/dp/B0H7BHDLP3"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.com/dp/B0H7S7DBCC"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0H4WXSXHS?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71KKtInj20L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0H4WXSXHS"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0H7BHDLP3"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.com/dp/B0H7S7DBCC?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ir2xpMGZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.com/dp/B0H7S7DBCC"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0H7BHDLP3?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Y82wY-+9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0H7BHDLP3"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0H7S7DBCC"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Z7yp-x1YL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0H7S7DBCC?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Ir2xpMGZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0H7S7DBCC"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/81Z7yp-x1YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HBQR6ZHF"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.comundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.com/dp/B0HFJCMP9T?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.com/dp/B0HFJCMP9T?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId241"/>
 </worksheet>
 </file>
 
